--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.14001516965779</v>
+        <v>1.972752465069392</v>
       </c>
       <c r="D2" t="n">
-        <v>9.487222151682225</v>
+        <v>1.541673599648362</v>
       </c>
       <c r="E2" t="n">
-        <v>6.955477847380549</v>
+        <v>1.130265150199339</v>
       </c>
       <c r="F2" t="n">
-        <v>7.004259765913991</v>
+        <v>1.138192211961024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.62781904944002</v>
+        <v>3.839520595534003</v>
       </c>
       <c r="D3" t="n">
-        <v>23.62781904944002</v>
+        <v>3.839520595534003</v>
       </c>
       <c r="E3" t="n">
-        <v>6.955477847380549</v>
+        <v>1.130265150199339</v>
       </c>
       <c r="F3" t="n">
-        <v>7.004259765913991</v>
+        <v>1.138192211961024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.29985933254184</v>
+        <v>3.623727141538049</v>
       </c>
       <c r="D4" t="n">
-        <v>21.58054244902757</v>
+        <v>3.506838147966981</v>
       </c>
       <c r="E4" t="n">
-        <v>6.955477847380549</v>
+        <v>1.130265150199339</v>
       </c>
       <c r="F4" t="n">
-        <v>7.004259765913991</v>
+        <v>1.138192211961024</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.26687680238663</v>
+        <v>1.180867480387827</v>
       </c>
       <c r="D5" t="n">
-        <v>7.774249693187241</v>
+        <v>1.263315575142927</v>
       </c>
       <c r="E5" t="n">
-        <v>6.955477847380549</v>
+        <v>1.130265150199339</v>
       </c>
       <c r="F5" t="n">
-        <v>7.004259765913991</v>
+        <v>1.138192211961024</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.17123981737892</v>
+        <v>1.327826470324075</v>
       </c>
       <c r="D6" t="n">
-        <v>7.995261641857948</v>
+        <v>1.299230016801917</v>
       </c>
       <c r="E6" t="n">
-        <v>6.955477847380549</v>
+        <v>1.130265150199339</v>
       </c>
       <c r="F6" t="n">
-        <v>7.004259765913991</v>
+        <v>1.138192211961024</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
